--- a/output/pdf_financials_xlsx/PLY.xlsx
+++ b/output/pdf_financials_xlsx/PLY.xlsx
@@ -4848,43 +4848,43 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.876621</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.638315</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.114709</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.326351</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.327488</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.327488</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.395778</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.274403</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.140667</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.126459</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.111139</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.834185</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.874386</v>
       </c>
     </row>
     <row r="93">
@@ -6031,43 +6031,43 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>1.571711</v>
+        <v>1.528387</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>5.764343</v>
+        <v>5.611568</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>2.993944</v>
+        <v>2.992644</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-0.470938</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-0.066</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0.90938</v>
+        <v>0.709391</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-0.205371</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-0.05608</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-1.196428</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-0.699201</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>3.215204</v>
+        <v>3.079308</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0.07255</v>
+        <v>0.02166</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-0.22433</v>
       </c>
     </row>
     <row r="119">
@@ -7751,7 +7751,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -7826,7 +7830,11 @@
           <t>Warrants reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -8456,7 +8464,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -9313,7 +9325,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -9994,7 +10010,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -10462,7 +10482,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -11029,7 +11053,11 @@
           <t>Reserves (Note 11)</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -11604,7 +11632,11 @@
           <t>Reserves (Note 12)</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E61" s="5" t="n">
         <v>0.876621</v>
       </c>
@@ -12223,7 +12255,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E70" s="5" t="n">
         <v>-0.043324</v>
       </c>

--- a/output/pdf_financials_xlsx/PLY.xlsx
+++ b/output/pdf_financials_xlsx/PLY.xlsx
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>4e-06</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0</v>
@@ -2009,34 +2009,34 @@
         <v>0</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.085809</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.000605</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.004798</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.010123</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.03233</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.122337</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.019391</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.003816</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.012885</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.472128</v>
       </c>
     </row>
     <row r="35">
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>4e-06</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0</v>
@@ -2101,34 +2101,34 @@
         <v>0</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.085809</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.000605</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.004798</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.010123</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.03233</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.122337</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.019391</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.003816</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.012885</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.472128</v>
       </c>
     </row>
     <row r="37">
@@ -2644,7 +2644,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>4e-06</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0</v>
@@ -2653,34 +2653,34 @@
         <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.085809</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.000605</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.007759</v>
+        <v>0.002961</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.078928</v>
+        <v>0.06880500000000001</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.05733</v>
+        <v>0.025</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.164625</v>
+        <v>0.042288</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.048128</v>
+        <v>0.028737</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.044149</v>
+        <v>0.040333</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.012885</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.477171</v>
+        <v>0.005043</v>
       </c>
     </row>
     <row r="49">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/PLY.xlsx
+++ b/output/pdf_financials_xlsx/PLY.xlsx
@@ -5893,7 +5893,7 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.001565</v>
       </c>
       <c r="C115" s="3" t="n">
         <v>0</v>
@@ -13002,7 +13002,11 @@
           <t>Private placement - - - - 60,000 45,000</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -22432,7 +22436,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E199" s="5" t="n">
         <v>0.001565</v>
       </c>
@@ -22673,7 +22681,11 @@
           <t>Private placement - - - - 20,500</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E202" s="5" t="n">
         <v>0.0205</v>
       </c>
